--- a/Result/profitability/8921.xlsx
+++ b/Result/profitability/8921.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04250000000000001</v>
+        <v>-0.10875</v>
       </c>
       <c r="N2" t="n">
-        <v>10.3375</v>
+        <v>10.06375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05000000000000001</v>
+        <v>-0.08625000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>10.40625</v>
+        <v>10.03875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.03250000000000001</v>
+        <v>-0.05875000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>10.0675</v>
+        <v>9.85</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.12</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003749999999999989</v>
+        <v>-0.02875000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>10.275</v>
+        <v>9.812500000000002</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02499999999999999</v>
+        <v>-0.04375000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>10.29125</v>
+        <v>9.893750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02499999999999999</v>
+        <v>-0.02250000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>10.52875</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,13 +1279,13 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04125</v>
+        <v>0.02625</v>
       </c>
       <c r="N8" t="n">
-        <v>10.495</v>
+        <v>10.63375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9828,6 +9828,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8921</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>160</v>
+      </c>
+      <c r="D75" t="n">
+        <v>147</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-13.06%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-25</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.08750000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.35875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4615384615384615</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.699999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3124999999999999</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
